--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\10冨田\2024\2024\unity\UNIFIGHT\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA0A1D5C-ED3A-4476-8FC6-09404D8EB0D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{704F2A37-615A-4E90-A4B6-823706C3CB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6420" yWindow="2640" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unit" sheetId="1" r:id="rId1"/>
@@ -440,7 +440,7 @@
         <v>1.2</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6">

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\10冨田\2024\2024\unity\UNIFIGHT\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{704F2A37-615A-4E90-A4B6-823706C3CB68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A4F0A1-ABDA-444D-AFA3-5AB14AD9101C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -396,11 +396,11 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
-    <col min="3" max="3" width="12.875" customWidth="1"/>
+    <col min="3" max="3" width="6.5" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="16.875" customWidth="1"/>
     <col min="6" max="6" width="16.125" customWidth="1"/>
-    <col min="7" max="7" width="9.5" customWidth="1"/>
+    <col min="7" max="7" width="22.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\10冨田\2024\2024\unity\UNIFIGHT\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A4F0A1-ABDA-444D-AFA3-5AB14AD9101C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99C84976-78B1-42E3-8AB5-5B7B9B91A9B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unit" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>A</t>
     <phoneticPr fontId="1"/>
@@ -67,6 +67,34 @@
   </si>
   <si>
     <t>speed</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>passive</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>skill1CoolTime</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>skill2CoolTime</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>urthCoolTime</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>skill1Duration</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>skill2Duration</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>urthDuration</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -392,18 +420,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
     <col min="3" max="3" width="6.5" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="16.875" customWidth="1"/>
-    <col min="6" max="6" width="16.125" customWidth="1"/>
-    <col min="7" max="7" width="22.75" customWidth="1"/>
+    <col min="6" max="6" width="8.5" customWidth="1"/>
+    <col min="7" max="7" width="8.25" customWidth="1"/>
+    <col min="8" max="8" width="16.625" customWidth="1"/>
+    <col min="9" max="9" width="14.375" customWidth="1"/>
+    <col min="10" max="10" width="15.5" customWidth="1"/>
+    <col min="11" max="11" width="15.75" customWidth="1"/>
+    <col min="12" max="13" width="12.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -422,8 +455,29 @@
       <c r="F1" t="s">
         <v>9</v>
       </c>
+      <c r="G1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:13">
       <c r="A2">
         <v>1</v>
       </c>
@@ -442,8 +496,29 @@
       <c r="F2">
         <v>10</v>
       </c>
+      <c r="G2">
+        <v>2.5</v>
+      </c>
+      <c r="H2">
+        <v>10.5</v>
+      </c>
+      <c r="I2">
+        <v>4.5</v>
+      </c>
+      <c r="J2">
+        <v>20</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:13">
       <c r="A3">
         <v>2</v>
       </c>
@@ -462,8 +537,29 @@
       <c r="F3">
         <v>5</v>
       </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <v>7</v>
+      </c>
+      <c r="J3">
+        <v>25.5</v>
+      </c>
+      <c r="K3">
+        <v>25.5</v>
+      </c>
+      <c r="L3">
+        <v>10</v>
+      </c>
+      <c r="M3">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:13">
       <c r="A4">
         <v>3</v>
       </c>
@@ -482,8 +578,29 @@
       <c r="F4">
         <v>5</v>
       </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4">
+        <v>7.5</v>
+      </c>
+      <c r="I4">
+        <v>9</v>
+      </c>
+      <c r="J4">
+        <v>15</v>
+      </c>
+      <c r="K4">
+        <v>20.5</v>
+      </c>
+      <c r="L4">
+        <v>20</v>
+      </c>
+      <c r="M4">
+        <v>15</v>
+      </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:13">
       <c r="A5">
         <v>4</v>
       </c>
@@ -501,6 +618,27 @@
       </c>
       <c r="F5">
         <v>5</v>
+      </c>
+      <c r="G5">
+        <v>3.5</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>4.5</v>
+      </c>
+      <c r="J5">
+        <v>20.5</v>
+      </c>
+      <c r="K5">
+        <v>10.5</v>
+      </c>
+      <c r="L5">
+        <v>10.5</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\10冨田\2024\2024\unity\UNIFIGHT\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99C84976-78B1-42E3-8AB5-5B7B9B91A9B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC24FC5-3D04-4769-977E-1B6A03471D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -512,7 +512,7 @@
         <v>5</v>
       </c>
       <c r="L2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -594,7 +594,7 @@
         <v>20.5</v>
       </c>
       <c r="L4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="M4">
         <v>15</v>
@@ -635,7 +635,7 @@
         <v>10.5</v>
       </c>
       <c r="L5">
-        <v>10.5</v>
+        <v>200</v>
       </c>
       <c r="M5">
         <v>0</v>

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\10冨田\2024\2024\unity\UNIFIGHT\Assets\TomitaFile\Status\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\Git\unifight\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC24FC5-3D04-4769-977E-1B6A03471D77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D57245D5-D79C-4D83-B2CA-53500334ED6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5115" yWindow="-13350" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unit" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>A</t>
     <phoneticPr fontId="1"/>
@@ -95,6 +95,14 @@
   </si>
   <si>
     <t>urthDuration</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Golem</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Length</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -420,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
@@ -641,6 +649,88 @@
         <v>0</v>
       </c>
     </row>
+    <row r="6" spans="1:13">
+      <c r="A6">
+        <v>100</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>10000</v>
+      </c>
+      <c r="D6">
+        <v>15</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6">
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <v>30</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\Git\unifight\Assets\TomitaFile\Status\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\10冨田\2024\2024\unity\UNIFIGHT\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D57245D5-D79C-4D83-B2CA-53500334ED6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA558F12-BACB-434D-BE67-078105B6CBA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5115" yWindow="-13350" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unit" sheetId="1" r:id="rId1"/>
@@ -102,7 +102,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Length</t>
+    <t>tower</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -698,7 +698,7 @@
         <v>18</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D7">
         <v>0</v>

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\10冨田\2024\2024\unity\UNIFIGHT\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA558F12-BACB-434D-BE67-078105B6CBA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA62C182-A3F1-4B1D-B7E3-A0B82FF06761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>A</t>
     <phoneticPr fontId="1"/>
@@ -103,6 +103,47 @@
   </si>
   <si>
     <t>tower</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Range</t>
+  </si>
+  <si>
+    <t>普通</t>
+    <rPh sb="0" eb="2">
+      <t>フツウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高速</t>
+    <rPh sb="0" eb="2">
+      <t>コウソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>低速</t>
+    <rPh sb="0" eb="2">
+      <t>テイソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>超高速</t>
+    <rPh sb="0" eb="1">
+      <t>チョウ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>コウソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>超低速</t>
+    <rPh sb="0" eb="3">
+      <t>チョウテイソク</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -428,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
@@ -442,9 +483,10 @@
     <col min="10" max="10" width="15.5" customWidth="1"/>
     <col min="11" max="11" width="15.75" customWidth="1"/>
     <col min="12" max="13" width="12.875" customWidth="1"/>
+    <col min="14" max="14" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -484,8 +526,11 @@
       <c r="M1" t="s">
         <v>16</v>
       </c>
+      <c r="N1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2">
         <v>1</v>
       </c>
@@ -525,8 +570,11 @@
       <c r="M2">
         <v>0</v>
       </c>
+      <c r="N2" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14">
       <c r="A3">
         <v>2</v>
       </c>
@@ -566,8 +614,11 @@
       <c r="M3">
         <v>10</v>
       </c>
+      <c r="N3" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:14">
       <c r="A4">
         <v>3</v>
       </c>
@@ -607,8 +658,11 @@
       <c r="M4">
         <v>15</v>
       </c>
+      <c r="N4" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:14">
       <c r="A5">
         <v>4</v>
       </c>
@@ -648,8 +702,11 @@
       <c r="M5">
         <v>0</v>
       </c>
+      <c r="N5" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:14">
       <c r="A6">
         <v>100</v>
       </c>
@@ -689,8 +746,11 @@
       <c r="M6">
         <v>0</v>
       </c>
+      <c r="N6" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:14">
       <c r="A7">
         <v>0</v>
       </c>
@@ -729,6 +789,9 @@
       </c>
       <c r="M7">
         <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\10冨田\2024\2024\unity\UNIFIGHT\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA62C182-A3F1-4B1D-B7E3-A0B82FF06761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74F4F7E-D853-4B6A-8583-C7EB9E733499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>A</t>
     <phoneticPr fontId="1"/>
@@ -109,41 +109,19 @@
     <t>Range</t>
   </si>
   <si>
-    <t>普通</t>
-    <rPh sb="0" eb="2">
-      <t>フツウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>高速</t>
-    <rPh sb="0" eb="2">
-      <t>コウソク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>低速</t>
-    <rPh sb="0" eb="2">
-      <t>テイソク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>超高速</t>
-    <rPh sb="0" eb="1">
-      <t>チョウ</t>
-    </rPh>
-    <rPh sb="1" eb="3">
-      <t>コウソク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>超低速</t>
-    <rPh sb="0" eb="3">
-      <t>チョウテイソク</t>
-    </rPh>
+    <t>LongDistance</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ShortDistance</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Usually</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SuperLongDistance</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -483,7 +461,8 @@
     <col min="10" max="10" width="15.5" customWidth="1"/>
     <col min="11" max="11" width="15.75" customWidth="1"/>
     <col min="12" max="13" width="12.875" customWidth="1"/>
-    <col min="14" max="14" width="12.625" customWidth="1"/>
+    <col min="14" max="14" width="19.25" customWidth="1"/>
+    <col min="15" max="15" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -571,7 +550,7 @@
         <v>0</v>
       </c>
       <c r="N2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -615,7 +594,7 @@
         <v>10</v>
       </c>
       <c r="N3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -659,7 +638,7 @@
         <v>15</v>
       </c>
       <c r="N4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -747,7 +726,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -791,7 +770,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\10冨田\2024\2024\unity\UNIFIGHT\Assets\TomitaFile\Status\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\Git\unifight\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74F4F7E-D853-4B6A-8583-C7EB9E733499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E8BD51-ED8A-481C-8509-BA919660B356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\Git\unifight\Assets\TomitaFile\Status\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\10冨田\2024\2024\unity\UNIFIGHT\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4E8BD51-ED8A-481C-8509-BA919660B356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15D2506-D91F-4A4D-A521-0E69D84581D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3795" yWindow="360" windowWidth="23445" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unit" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
   <si>
     <t>A</t>
     <phoneticPr fontId="1"/>
@@ -109,19 +109,69 @@
     <t>Range</t>
   </si>
   <si>
-    <t>LongDistance</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ShortDistance</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Usually</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>SuperLongDistance</t>
+    <t>短距離</t>
+    <rPh sb="0" eb="3">
+      <t>タンキョリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>普通</t>
+    <rPh sb="0" eb="2">
+      <t>フツウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>長距離</t>
+    <rPh sb="0" eb="3">
+      <t>チョウキョリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>超長距離</t>
+    <rPh sb="0" eb="1">
+      <t>チョウ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キョリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高速</t>
+    <rPh sb="0" eb="2">
+      <t>コウソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>超低速</t>
+    <rPh sb="0" eb="3">
+      <t>チョウテイソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>超高速</t>
+    <rPh sb="0" eb="3">
+      <t>チョウコウソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>低速</t>
+    <rPh sb="0" eb="2">
+      <t>テイソク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>speedText</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -447,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
@@ -465,7 +515,7 @@
     <col min="15" max="15" width="15.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -508,8 +558,11 @@
       <c r="N1" t="s">
         <v>19</v>
       </c>
+      <c r="O1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -550,10 +603,13 @@
         <v>0</v>
       </c>
       <c r="N2" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="O2" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -594,10 +650,13 @@
         <v>10</v>
       </c>
       <c r="N3" t="s">
+        <v>20</v>
+      </c>
+      <c r="O3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>3</v>
       </c>
@@ -638,10 +697,13 @@
         <v>15</v>
       </c>
       <c r="N4" t="s">
-        <v>22</v>
+        <v>21</v>
+      </c>
+      <c r="O4" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -682,10 +744,13 @@
         <v>0</v>
       </c>
       <c r="N5" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="O5" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>100</v>
       </c>
@@ -726,10 +791,13 @@
         <v>0</v>
       </c>
       <c r="N6" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="O6" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>0</v>
       </c>
@@ -770,7 +838,10 @@
         <v>0</v>
       </c>
       <c r="N7" t="s">
-        <v>22</v>
+        <v>21</v>
+      </c>
+      <c r="O7" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\10冨田\2024\2024\unity\UNIFIGHT\Assets\TomitaFile\Status\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\Git\unifight\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F15D2506-D91F-4A4D-A521-0E69D84581D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD6CAC8-D63E-4714-A24C-C557B18E6FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3795" yWindow="360" windowWidth="23445" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5115" yWindow="-13350" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unit" sheetId="1" r:id="rId1"/>
@@ -758,7 +758,7 @@
         <v>17</v>
       </c>
       <c r="C6">
-        <v>10000</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <v>15</v>

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\Git\unifight\Assets\TomitaFile\Status\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024 重川\Github\UNIFIGHT\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD6CAC8-D63E-4714-A24C-C557B18E6FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78ACAEB-E60B-4F9A-8A4E-6334ABFCF7A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5115" yWindow="-13350" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unit" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
   <si>
     <t>A</t>
     <phoneticPr fontId="1"/>
@@ -172,6 +172,14 @@
   </si>
   <si>
     <t>speedText</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Turret</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なし</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -497,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
@@ -844,6 +852,53 @@
         <v>21</v>
       </c>
     </row>
+    <row r="8" spans="1:15">
+      <c r="A8">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>30</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>21</v>
+      </c>
+      <c r="O8" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024 重川\Github\UNIFIGHT\Assets\TomitaFile\Status\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\10冨田\2024\2024\unity\UNIFIGHT\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78ACAEB-E60B-4F9A-8A4E-6334ABFCF7A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3E9975-BF2A-494A-9D5C-DE907A124F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unit" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
   <si>
     <t>A</t>
     <phoneticPr fontId="1"/>
@@ -180,6 +180,10 @@
   </si>
   <si>
     <t>なし</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mushroom</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -505,7 +509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
@@ -807,22 +811,22 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C7">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -849,7 +853,7 @@
         <v>21</v>
       </c>
       <c r="O7" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -857,16 +861,16 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D8">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -896,6 +900,53 @@
         <v>21</v>
       </c>
       <c r="O8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9">
+        <v>0</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>30</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>21</v>
+      </c>
+      <c r="O9" t="s">
         <v>30</v>
       </c>
     </row>

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\10冨田\2024\2024\unity\UNIFIGHT\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3E9975-BF2A-494A-9D5C-DE907A124F38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2704F7A4-EA94-40FF-8D44-C9A79A224157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5280" yWindow="1575" windowWidth="23445" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unit" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
   <si>
     <t>A</t>
     <phoneticPr fontId="1"/>
@@ -184,6 +184,10 @@
   </si>
   <si>
     <t>mushroom</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cactus</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -509,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
@@ -858,22 +862,22 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="C8">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -900,7 +904,7 @@
         <v>21</v>
       </c>
       <c r="O8" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -908,16 +912,16 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D9">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -947,6 +951,53 @@
         <v>21</v>
       </c>
       <c r="O9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>30</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>21</v>
+      </c>
+      <c r="O10" t="s">
         <v>30</v>
       </c>
     </row>

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\10冨田\2024\2024\unity\UNIFIGHT\Assets\TomitaFile\Status\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\Git\unifight\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2704F7A4-EA94-40FF-8D44-C9A79A224157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0FED9AA-EF75-4057-AFC9-16EC7E260FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5280" yWindow="1575" windowWidth="23445" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5115" yWindow="-13350" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unit" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
   <si>
     <t>A</t>
     <phoneticPr fontId="1"/>
@@ -184,10 +184,6 @@
   </si>
   <si>
     <t>mushroom</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Cactus</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -513,7 +509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
@@ -774,7 +770,7 @@
         <v>17</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>10000</v>
       </c>
       <c r="D6">
         <v>15</v>
@@ -862,22 +858,22 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -904,7 +900,7 @@
         <v>21</v>
       </c>
       <c r="O8" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -912,16 +908,16 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C9">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -951,53 +947,6 @@
         <v>21</v>
       </c>
       <c r="O9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10">
-        <v>0</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>30</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>21</v>
-      </c>
-      <c r="O10" t="s">
         <v>30</v>
       </c>
     </row>

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\Git\unifight\Assets\TomitaFile\Status\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\10冨田\2024\2024\unity\UNIFIGHT\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0FED9AA-EF75-4057-AFC9-16EC7E260FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACF60A9A-43B9-499E-91A7-0900037664E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5115" yWindow="-13350" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1575" windowWidth="23445" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unit" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
   <si>
     <t>A</t>
     <phoneticPr fontId="1"/>
@@ -183,7 +183,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>mushroom</t>
+    <t>Cactus</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Mushroom</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -509,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
@@ -814,7 +818,7 @@
         <v>101</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <v>10</v>
@@ -858,22 +862,22 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="C8">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -897,10 +901,10 @@
         <v>0</v>
       </c>
       <c r="N8" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="O8" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -908,16 +912,16 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D9">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -947,6 +951,53 @@
         <v>21</v>
       </c>
       <c r="O9" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>30</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>21</v>
+      </c>
+      <c r="O10" t="s">
         <v>30</v>
       </c>
     </row>

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\10冨田\2024\2024\unity\UNIFIGHT\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACF60A9A-43B9-499E-91A7-0900037664E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5786735-5B1D-466F-8EEE-5D6D6ED8BF9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1575" windowWidth="23445" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
   <si>
     <t>A</t>
     <phoneticPr fontId="1"/>
@@ -188,6 +188,14 @@
   </si>
   <si>
     <t>Mushroom</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Necro</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>skelton</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -513,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
@@ -818,31 +826,31 @@
         <v>101</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -854,7 +862,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="O7" t="s">
         <v>30</v>
@@ -865,19 +873,19 @@
         <v>102</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C8">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -909,22 +917,22 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="C9">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -951,53 +959,147 @@
         <v>21</v>
       </c>
       <c r="O9" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11">
+        <v>1000</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>21</v>
+      </c>
+      <c r="O11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
         <v>29</v>
       </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>30</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>30</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
         <v>21</v>
       </c>
-      <c r="O10" t="s">
+      <c r="O12" t="s">
         <v>30</v>
       </c>
     </row>

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\10冨田\2024\2024\unity\UNIFIGHT\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5786735-5B1D-466F-8EEE-5D6D6ED8BF9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0D321C7-07E0-4E90-8CEB-58CC9D59AFA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1575" windowWidth="23445" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unit" sheetId="1" r:id="rId1"/>
@@ -30,22 +30,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
   <si>
-    <t>A</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>B</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>C</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>D</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>hp</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -196,6 +180,22 @@
   </si>
   <si>
     <t>skelton</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Asult</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ShotGun</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Sniper</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Healer</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -541,49 +541,49 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="E1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="H1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="I1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="J1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>15</v>
       </c>
-      <c r="M1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N1" t="s">
-        <v>19</v>
-      </c>
       <c r="O1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:15">
@@ -591,7 +591,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -627,10 +627,10 @@
         <v>0</v>
       </c>
       <c r="N2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="O2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -638,7 +638,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C3">
         <v>50</v>
@@ -674,10 +674,10 @@
         <v>10</v>
       </c>
       <c r="N3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="O3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -685,7 +685,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="C4">
         <v>60</v>
@@ -721,10 +721,10 @@
         <v>15</v>
       </c>
       <c r="N4" t="s">
+        <v>17</v>
+      </c>
+      <c r="O4" t="s">
         <v>21</v>
-      </c>
-      <c r="O4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -732,7 +732,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C5">
         <v>30</v>
@@ -768,10 +768,10 @@
         <v>0</v>
       </c>
       <c r="N5" t="s">
+        <v>18</v>
+      </c>
+      <c r="O5" t="s">
         <v>22</v>
-      </c>
-      <c r="O5" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -779,7 +779,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C6">
         <v>10000</v>
@@ -815,10 +815,10 @@
         <v>0</v>
       </c>
       <c r="N6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="O6" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -826,7 +826,7 @@
         <v>101</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>1000</v>
@@ -862,10 +862,10 @@
         <v>0</v>
       </c>
       <c r="N7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="O7" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -873,7 +873,7 @@
         <v>102</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <v>50</v>
@@ -909,10 +909,10 @@
         <v>0</v>
       </c>
       <c r="N8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="O8" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -920,7 +920,7 @@
         <v>103</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C9">
         <v>10</v>
@@ -956,10 +956,10 @@
         <v>0</v>
       </c>
       <c r="N9" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="O9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -967,7 +967,7 @@
         <v>104</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C10">
         <v>10</v>
@@ -1003,10 +1003,10 @@
         <v>0</v>
       </c>
       <c r="N10" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="O10" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -1014,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C11">
         <v>1000</v>
@@ -1050,10 +1050,10 @@
         <v>0</v>
       </c>
       <c r="N11" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="O11" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -1061,7 +1061,7 @@
         <v>0</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1097,10 +1097,10 @@
         <v>0</v>
       </c>
       <c r="N12" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="O12" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\10冨田\2024\2024\unity\UNIFIGHT\Assets\TomitaFile\Status\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\Git\unifight\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0D321C7-07E0-4E90-8CEB-58CC9D59AFA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20019EF6-EA48-4EE3-B4D2-C402A4C7B235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6150" yWindow="-12315" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unit" sheetId="1" r:id="rId1"/>
@@ -644,7 +644,7 @@
         <v>50</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -691,7 +691,7 @@
         <v>60</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="E4">
         <v>2.5</v>
@@ -738,7 +738,7 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="E5">
         <v>1.3</v>

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\Git\unifight\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20019EF6-EA48-4EE3-B4D2-C402A4C7B235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E2B4FA-DBE2-44A8-B376-C71FFAE7FAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6150" yWindow="-12315" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -594,7 +594,7 @@
         <v>31</v>
       </c>
       <c r="C2">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="D2">
         <v>100</v>

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\Git\unifight\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E2B4FA-DBE2-44A8-B376-C71FFAE7FAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAEF36C8-C915-4CF8-82BB-D77371D17219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6150" yWindow="-12315" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -603,7 +603,7 @@
         <v>1.2</v>
       </c>
       <c r="F2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>2.5</v>
@@ -697,7 +697,7 @@
         <v>2.5</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -744,7 +744,7 @@
         <v>1.3</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G5">
         <v>3.5</v>

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\Git\unifight\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAEF36C8-C915-4CF8-82BB-D77371D17219}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DADB2EF5-43D5-4AF3-93C3-159C9EE5DD8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6150" yWindow="-12315" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="37">
   <si>
     <t>hp</t>
     <phoneticPr fontId="1"/>
@@ -196,6 +196,17 @@
   </si>
   <si>
     <t>Healer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Bomb</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遅い</t>
+    <rPh sb="0" eb="1">
+      <t>オソ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -521,7 +532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
@@ -1103,6 +1114,53 @@
         <v>26</v>
       </c>
     </row>
+    <row r="13" spans="1:15">
+      <c r="A13">
+        <v>105</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13">
+        <v>150</v>
+      </c>
+      <c r="D13">
+        <v>100</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>26</v>
+      </c>
+      <c r="O13" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\Git\unifight\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DADB2EF5-43D5-4AF3-93C3-159C9EE5DD8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E97ED0-CE08-45B3-83DE-255557054163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6150" yWindow="-12315" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -755,7 +755,7 @@
         <v>1.3</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G5">
         <v>3.5</v>

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\Git\unifight\Assets\TomitaFile\Status\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\UNIFIGHT\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E97ED0-CE08-45B3-83DE-255557054163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35B4CC09-059E-4BFF-9FEF-11778AE9D64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6150" yWindow="-12315" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3750" yWindow="585" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unit" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="38">
   <si>
     <t>hp</t>
     <phoneticPr fontId="1"/>
@@ -207,6 +207,10 @@
     <rPh sb="0" eb="1">
       <t>オソ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Wyburn</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -532,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
@@ -1161,6 +1165,53 @@
         <v>36</v>
       </c>
     </row>
+    <row r="14" spans="1:15">
+      <c r="A14">
+        <v>106</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14">
+        <v>10000</v>
+      </c>
+      <c r="D14">
+        <v>20</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>17</v>
+      </c>
+      <c r="O14" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\UNIFIGHT\Assets\TomitaFile\Status\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\Git\unifight\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35B4CC09-059E-4BFF-9FEF-11778AE9D64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E11EB5-3B74-4AE2-9F24-0140A433A2D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3750" yWindow="585" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6150" yWindow="-12315" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unit" sheetId="1" r:id="rId1"/>
@@ -806,7 +806,7 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6">
         <v>0</v>

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\Git\unifight\Assets\TomitaFile\Status\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\UNIFIGHT\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E11EB5-3B74-4AE2-9F24-0140A433A2D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBFDE191-3F69-4880-BD0F-D1A168EA7B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6150" yWindow="-12315" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3750" yWindow="585" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unit" sheetId="1" r:id="rId1"/>
@@ -1173,7 +1173,7 @@
         <v>37</v>
       </c>
       <c r="C14">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="D14">
         <v>20</v>

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\UNIFIGHT\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBFDE191-3F69-4880-BD0F-D1A168EA7B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFDDBB19-097D-4018-98C1-8E71AC9D46F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3750" yWindow="585" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1173,7 +1173,7 @@
         <v>37</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="D14">
         <v>20</v>

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\UNIFIGHT\Assets\TomitaFile\Status\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024 重川\Github\UNIFIGHT\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFDDBB19-097D-4018-98C1-8E71AC9D46F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8FB6A2E-D33D-4657-930C-E5877C866622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3750" yWindow="585" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unit" sheetId="1" r:id="rId1"/>
@@ -618,16 +618,16 @@
         <v>1.2</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G2">
         <v>2.5</v>
       </c>
       <c r="H2">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="I2">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="J2">
         <v>20</v>
@@ -656,7 +656,7 @@
         <v>32</v>
       </c>
       <c r="C3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D3">
         <v>100</v>
@@ -665,7 +665,7 @@
         <v>2</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G3">
         <v>1</v>
@@ -674,7 +674,7 @@
         <v>8</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J3">
         <v>25.5</v>
@@ -706,22 +706,22 @@
         <v>60</v>
       </c>
       <c r="D4">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E4">
         <v>2.5</v>
       </c>
       <c r="F4">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G4">
         <v>2</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>20</v>
       </c>
       <c r="I4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J4">
         <v>15</v>
@@ -750,7 +750,7 @@
         <v>33</v>
       </c>
       <c r="C5">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D5">
         <v>100</v>
@@ -765,10 +765,10 @@
         <v>3.5</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="J5">
         <v>20.5</v>
@@ -797,10 +797,10 @@
         <v>13</v>
       </c>
       <c r="C6">
-        <v>10000</v>
+        <v>7500</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1176,7 +1176,7 @@
         <v>10000</v>
       </c>
       <c r="D14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E14">
         <v>1</v>

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024 重川\Github\UNIFIGHT\Assets\TomitaFile\Status\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\UNIFIGHT\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8FB6A2E-D33D-4657-930C-E5877C866622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125BDB8C-6671-4FB7-937D-A5F6A12D9331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3750" yWindow="585" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unit" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="39">
   <si>
     <t>hp</t>
     <phoneticPr fontId="1"/>
@@ -211,6 +211,10 @@
   </si>
   <si>
     <t>Wyburn</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Robot</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -536,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="2" max="2" width="10.125" customWidth="1"/>
@@ -609,7 +613,7 @@
         <v>31</v>
       </c>
       <c r="C2">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="D2">
         <v>100</v>
@@ -1209,6 +1213,53 @@
         <v>17</v>
       </c>
       <c r="O14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15">
+        <v>107</v>
+      </c>
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15">
+        <v>1000</v>
+      </c>
+      <c r="D15">
+        <v>20</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>17</v>
+      </c>
+      <c r="O15" t="s">
         <v>26</v>
       </c>
     </row>

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024\UNIFIGHT\Assets\TomitaFile\Status\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024 重川\Github\UNIFIGHT\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125BDB8C-6671-4FB7-937D-A5F6A12D9331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A80F49EC-E250-4612-A8C6-A082E911D2D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3750" yWindow="585" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2070" yWindow="-13650" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unit" sheetId="1" r:id="rId1"/>
@@ -710,7 +710,7 @@
         <v>60</v>
       </c>
       <c r="D4">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="E4">
         <v>2.5</v>

--- a/Assets/TomitaFile/Status/StatusParameter.xlsx
+++ b/Assets/TomitaFile/Status/StatusParameter.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2024 重川\Github\UNIFIGHT\Assets\TomitaFile\Status\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A80F49EC-E250-4612-A8C6-A082E911D2D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A619E9F3-5634-4425-8128-AD386089E0C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2070" yWindow="-13650" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2070" yWindow="2550" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Unit" sheetId="1" r:id="rId1"/>
